--- a/artfynd/A 61722-2023 artfynd.xlsx
+++ b/artfynd/A 61722-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61722-2023 artfynd.xlsx
+++ b/artfynd/A 61722-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118117700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Visten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>410490</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6613977</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Blir bortjagade av grå flugsnappare som har bo med 5 snart flygfärdiga ungar på vårt hus.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61722-2023 artfynd.xlsx
+++ b/artfynd/A 61722-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,128 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126393503</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58485</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Visten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410490</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6613977</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61722-2023 artfynd.xlsx
+++ b/artfynd/A 61722-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>126393503</v>
       </c>
       <c r="B4" t="n">
-        <v>58485</v>
+        <v>58488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
